--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83454</v>
+        <v>83458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83458</v>
+        <v>83460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83461</v>
+        <v>83465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83465</v>
+        <v>83467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83467</v>
+        <v>83480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136769406</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136769407</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136769397</v>
       </c>
       <c r="B12" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83480</v>
+        <v>83482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136769406</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136769407</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136769397</v>
       </c>
       <c r="B12" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -1610,11 +1610,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -1732,11 +1728,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -1858,11 +1850,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83482</v>
+        <v>83485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83485</v>
+        <v>83495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136769406</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136769407</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136769397</v>
       </c>
       <c r="B12" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -1937,7 +1937,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769401</v>
       </c>
       <c r="B2" t="n">
-        <v>83495</v>
+        <v>83498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769396</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769398</v>
       </c>
       <c r="B4" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769399</v>
       </c>
       <c r="B5" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769402</v>
       </c>
       <c r="B6" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769403</v>
       </c>
       <c r="B7" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769404</v>
       </c>
       <c r="B8" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136769405</v>
       </c>
       <c r="B9" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136769406</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136769407</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136769397</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 5127-2024 artfynd.xlsx
+++ b/artfynd/S 5127-2024 artfynd.xlsx
@@ -1937,7 +1937,7 @@
         <v>136769400</v>
       </c>
       <c r="B13" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
